--- a/Result/profitability/4904.xlsx
+++ b/Result/profitability/4904.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.72</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9312499999999999</v>
+        <v>0.96</v>
       </c>
       <c r="N2" t="n">
-        <v>32.99</v>
+        <v>32.8725</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0.84</v>
       </c>
       <c r="M3" t="n">
-        <v>0.92625</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>34.79375</v>
+        <v>35.07125</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.8</v>
       </c>
       <c r="M4" t="n">
-        <v>0.90125</v>
+        <v>0.9275000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>36.90125</v>
+        <v>36.8275</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.7</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8762500000000001</v>
+        <v>0.8975</v>
       </c>
       <c r="N5" t="n">
-        <v>38.7975</v>
+        <v>38.6975</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.71</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8475</v>
+        <v>0.86625</v>
       </c>
       <c r="N6" t="n">
-        <v>40.41125</v>
+        <v>40.5</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.71</v>
       </c>
       <c r="M7" t="n">
-        <v>0.81625</v>
+        <v>0.8275</v>
       </c>
       <c r="N7" t="n">
-        <v>41.99</v>
+        <v>42.56625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.73</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7799999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="N8" t="n">
-        <v>44.19875</v>
+        <v>44.035</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7375</v>
+        <v>0.7374999999999999</v>
       </c>
       <c r="N9" t="n">
         <v>45.715</v>
@@ -1772,7 +1772,7 @@
         <v>0.6</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7062499999999999</v>
+        <v>0.70625</v>
       </c>
       <c r="N11" t="n">
         <v>44.65125</v>
@@ -9332,30 +9332,30 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>24540</v>
+        <v>26105</v>
       </c>
       <c r="D71" t="n">
-        <v>16777</v>
+        <v>17641</v>
       </c>
       <c r="E71" t="n">
-        <v>7764</v>
+        <v>8465</v>
       </c>
       <c r="F71" t="n">
-        <v>31.64</v>
+        <v>32.42</v>
       </c>
       <c r="G71" t="n">
-        <v>4130</v>
+        <v>4316</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>16.83%</t>
+          <t>16.53%</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>-12</v>
+        <v>-45</v>
       </c>
       <c r="J71" t="n">
-        <v>4118</v>
+        <v>4272</v>
       </c>
       <c r="K71" t="n">
         <v>3374</v>
@@ -9367,7 +9367,7 @@
         <v>0.89375</v>
       </c>
       <c r="N71" t="n">
-        <v>30.875</v>
+        <v>30.9725</v>
       </c>
       <c r="O71" t="n">
         <v>1</v>
@@ -9400,10 +9400,10 @@
         <v>0.04444444444444429</v>
       </c>
       <c r="Y71" t="n">
-        <v>-0.5700000000000003</v>
+        <v>0.2100000000000009</v>
       </c>
       <c r="Z71" t="n">
-        <v>-0.01769636758770565</v>
+        <v>0.006519714374418006</v>
       </c>
       <c r="AA71" t="n">
         <v>0.06999999999999995</v>
@@ -9412,10 +9412,10 @@
         <v>0.08045977011494254</v>
       </c>
       <c r="AC71" t="n">
-        <v>0.01000000000000156</v>
+        <v>0.7900000000000027</v>
       </c>
       <c r="AD71" t="n">
-        <v>0.0003161555485298173</v>
+        <v>0.02497628833386045</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -9424,7 +9424,7 @@
         <v>1</v>
       </c>
       <c r="AG71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH71" t="n">
         <v>1</v>
@@ -9459,30 +9459,30 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>26394</v>
+        <v>24829</v>
       </c>
       <c r="D72" t="n">
-        <v>18212</v>
+        <v>17347</v>
       </c>
       <c r="E72" t="n">
-        <v>8182</v>
+        <v>7481</v>
       </c>
       <c r="F72" t="n">
-        <v>31</v>
+        <v>30.13</v>
       </c>
       <c r="G72" t="n">
-        <v>4183</v>
+        <v>3996</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>15.85%</t>
+          <t>16.10%</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>86</v>
+        <v>119</v>
       </c>
       <c r="J72" t="n">
-        <v>4270</v>
+        <v>4116</v>
       </c>
       <c r="K72" t="n">
         <v>3448</v>
@@ -9494,7 +9494,7 @@
         <v>0.905</v>
       </c>
       <c r="N72" t="n">
-        <v>30.90375</v>
+        <v>30.8925</v>
       </c>
       <c r="O72" t="n">
         <v>1</v>
@@ -9527,10 +9527,10 @@
         <v>0.02127659574468077</v>
       </c>
       <c r="Y72" t="n">
-        <v>-0.6400000000000006</v>
+        <v>-2.290000000000003</v>
       </c>
       <c r="Z72" t="n">
-        <v>-0.02022756005056892</v>
+        <v>-0.07063541024059228</v>
       </c>
       <c r="AA72" t="n">
         <v>0.07999999999999996</v>
@@ -9539,10 +9539,10 @@
         <v>0.09090909090909083</v>
       </c>
       <c r="AC72" t="n">
-        <v>-1.560000000000002</v>
+        <v>-2.430000000000003</v>
       </c>
       <c r="AD72" t="n">
-        <v>-0.04791154791154795</v>
+        <v>-0.07463144963144974</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -9621,7 +9621,7 @@
         <v>0.9237500000000001</v>
       </c>
       <c r="N73" t="n">
-        <v>30.7225</v>
+        <v>30.71125</v>
       </c>
       <c r="O73" t="n">
         <v>1</v>
@@ -9654,10 +9654,10 @@
         <v>0.0625</v>
       </c>
       <c r="Y73" t="n">
-        <v>-3.899999999999999</v>
+        <v>-3.029999999999998</v>
       </c>
       <c r="Z73" t="n">
-        <v>-0.1258064516129032</v>
+        <v>-0.1005642217059408</v>
       </c>
       <c r="AA73" t="n">
         <v>0.02000000000000002</v>
@@ -9748,7 +9748,7 @@
         <v>0.95</v>
       </c>
       <c r="N74" t="n">
-        <v>31.07</v>
+        <v>31.05875</v>
       </c>
       <c r="O74" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4904</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>28664</v>
+      </c>
+      <c r="D75" t="n">
+        <v>19575</v>
+      </c>
+      <c r="E75" t="n">
+        <v>9089</v>
+      </c>
+      <c r="F75" t="n">
+        <v>31.71</v>
+      </c>
+      <c r="G75" t="n">
+        <v>5023</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>17.52%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>133</v>
+      </c>
+      <c r="J75" t="n">
+        <v>5156</v>
+      </c>
+      <c r="K75" t="n">
+        <v>4009</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="N75" t="n">
+        <v>31.06875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.07766990291262132</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.310000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.03967292549969725</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.1700000000000002</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.1808510638297873</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.7100000000000009</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.02190006169031466</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
